--- a/ig/DM-JUILLET-2025/ValueSet-JDV-J34-CategorieOrganisation-ROR.xlsx
+++ b/ig/DM-JUILLET-2025/ValueSet-JDV-J34-CategorieOrganisation-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250710120000</t>
+    <t>20250723120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-10T12:00:00+01:00</t>
+    <t>2025-07-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -480,7 +480,7 @@
     <t>65</t>
   </si>
   <si>
-    <t>Pôles de compétences et de prestations externalisées (PCPE)</t>
+    <t>Pôle de compétences et de prestations externalisées (PCPE)</t>
   </si>
   <si>
     <t>66</t>
@@ -1512,7 +1512,7 @@
     <t>238</t>
   </si>
   <si>
-    <t>Unité de médecine polyvalente</t>
+    <t>Unité hospitalière de médecine polyvalente</t>
   </si>
   <si>
     <t>239</t>
